--- a/assets/calculateur-prix-modele-en.xlsx
+++ b/assets/calculateur-prix-modele-en.xlsx
@@ -60,7 +60,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;€&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">

--- a/assets/calculateur-prix-modele-en.xlsx
+++ b/assets/calculateur-prix-modele-en.xlsx
@@ -37,16 +37,16 @@
     <t>Desired markup</t>
   </si>
   <si>
-    <t>VAT</t>
+    <t>Sales tax (GST + QST)</t>
   </si>
   <si>
     <t>Cost price</t>
   </si>
   <si>
-    <t>Selling price excl. VAT</t>
-  </si>
-  <si>
-    <t>Selling price incl. VAT</t>
+    <t>Selling price before tax</t>
+  </si>
+  <si>
+    <t>Selling price with tax</t>
   </si>
   <si>
     <t>Profit per product</t>
@@ -59,9 +59,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0##%"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -130,10 +131,11 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,51 +547,51 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6">
-        <v>0.2</v>
+      <c r="B8" s="7">
+        <v>0.14975</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <f>B3+B4/60*B5+B6</f>
         <v>14.58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="9">
         <f>B10*(1+B7)</f>
         <v>21.87</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <f>B11*(1+B8)</f>
-        <v>26.244</v>
+        <v>25.145032500000003</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>B11-B10</f>
         <v>7.290000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <f>B13/B11</f>
         <v>0.33333333333333337</v>
       </c>
@@ -602,7 +604,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B8">
-      <formula1>"0.055,0.1,0.2"</formula1>
+      <formula1>"0.14975,0.05,0.13,0.15"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
